--- a/full/sliding_window_results_window_7.xlsx
+++ b/full/sliding_window_results_window_7.xlsx
@@ -463,13 +463,13 @@
         <v>29.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>30.40247058788219</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.75</v>
+        <v>0.6524705878821884</v>
       </c>
       <c r="E2" t="n">
-        <v>885.0625</v>
+        <v>0.4257178680513285</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.84</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29.84945777265597</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.84</v>
+        <v>0.009457772655970587</v>
       </c>
       <c r="E3" t="n">
-        <v>890.4256</v>
+        <v>8.944946361202493e-05</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.81</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>29.66142247796292</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.81</v>
+        <v>-0.1485775220370762</v>
       </c>
       <c r="E4" t="n">
-        <v>888.6360999999999</v>
+        <v>0.02207528005467786</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.92</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.5982817534586</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.92</v>
+        <v>-0.3217182465414048</v>
       </c>
       <c r="E5" t="n">
-        <v>895.2064000000001</v>
+        <v>0.1035026301576761</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.98</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>29.85312025586845</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.98</v>
+        <v>-0.1268797441315463</v>
       </c>
       <c r="E6" t="n">
-        <v>898.8004000000001</v>
+        <v>0.01609846947088667</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.04</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.06600351530143</v>
       </c>
       <c r="D7" t="n">
-        <v>-30.04</v>
+        <v>0.02600351530143286</v>
       </c>
       <c r="E7" t="n">
-        <v>902.4015999999999</v>
+        <v>0.0006761828080318527</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.21</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.34908901132387</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.21</v>
+        <v>0.1390890113238719</v>
       </c>
       <c r="E8" t="n">
-        <v>912.6441000000001</v>
+        <v>0.01934575307105215</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.22</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.52594039433468</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.22</v>
+        <v>0.3059403943346766</v>
       </c>
       <c r="E9" t="n">
-        <v>913.2483999999999</v>
+        <v>0.0935995248856574</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.38</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.35365911871458</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.38</v>
+        <v>-0.02634088128542089</v>
       </c>
       <c r="E10" t="n">
-        <v>922.9444</v>
+        <v>0.0006938420268926366</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.44</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.43898411740251</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.44</v>
+        <v>-0.001015882597489082</v>
       </c>
       <c r="E11" t="n">
-        <v>926.5936</v>
+        <v>1.032017451881164e-06</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.48</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.55094216973905</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.48</v>
+        <v>0.07094216973904466</v>
       </c>
       <c r="E12" t="n">
-        <v>929.0304</v>
+        <v>0.005032791447283424</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.69</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.68086014304607</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.69</v>
+        <v>-0.009139856953929382</v>
       </c>
       <c r="E13" t="n">
-        <v>941.8761000000001</v>
+        <v>8.353698513829128e-05</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.75</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.27902283158048</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.75</v>
+        <v>-0.4709771684195232</v>
       </c>
       <c r="E14" t="n">
-        <v>945.5625</v>
+        <v>0.2218194931724719</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.94</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.38232876759964</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.94</v>
+        <v>-0.557671232400363</v>
       </c>
       <c r="E15" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3109972034469397</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.95</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>30.69458768077862</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.95</v>
+        <v>-0.2554123192213815</v>
       </c>
       <c r="E16" t="n">
-        <v>957.9024999999999</v>
+        <v>0.06523545281004489</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.02</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>31.06272285481336</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.02</v>
+        <v>0.04272285481335913</v>
       </c>
       <c r="E17" t="n">
-        <v>962.2404</v>
+        <v>0.001825242323403364</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>31.35281011065088</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.12</v>
+        <v>0.2328101106508811</v>
       </c>
       <c r="E18" t="n">
-        <v>968.4544000000001</v>
+        <v>0.0542005476212755</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.28</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31.33141430812179</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.28</v>
+        <v>0.05141430812179237</v>
       </c>
       <c r="E19" t="n">
-        <v>978.4384000000001</v>
+        <v>0.002643431079642605</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.38</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31.6087785071903</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.38</v>
+        <v>0.2287785071902988</v>
       </c>
       <c r="E20" t="n">
-        <v>984.7044</v>
+        <v>0.0523396053522216</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.58</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.92626103420487</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.58</v>
+        <v>0.3462610342048755</v>
       </c>
       <c r="E21" t="n">
-        <v>997.2963999999999</v>
+        <v>0.11989670380863</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.65</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.9100204118511</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.65</v>
+        <v>0.2600204118511016</v>
       </c>
       <c r="E22" t="n">
-        <v>1001.7225</v>
+        <v>0.06761061457921649</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.88</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.59474956815411</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.88</v>
+        <v>-0.2852504318458919</v>
       </c>
       <c r="E23" t="n">
-        <v>1016.3344</v>
+        <v>0.08136780886826785</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.28</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>32.11077502296926</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.28</v>
+        <v>-0.1692249770307441</v>
       </c>
       <c r="E24" t="n">
-        <v>1041.9984</v>
+        <v>0.02863709285105588</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.45</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>32.1607344515993</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.45</v>
+        <v>-0.2892655484007065</v>
       </c>
       <c r="E25" t="n">
-        <v>1053.0025</v>
+        <v>0.08367455749156148</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.85</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>33.26761652402123</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.85</v>
+        <v>0.4176165240212271</v>
       </c>
       <c r="E26" t="n">
-        <v>1079.1225</v>
+        <v>0.1744035611355721</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.9</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>32.95359507319187</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.9</v>
+        <v>0.05359507319187173</v>
       </c>
       <c r="E27" t="n">
-        <v>1082.41</v>
+        <v>0.002872431870442088</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>33.28701813607838</v>
       </c>
       <c r="D28" t="n">
-        <v>-33.1</v>
+        <v>0.1870181360783789</v>
       </c>
       <c r="E28" t="n">
-        <v>1095.61</v>
+        <v>0.03497578322223106</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>33.29908565264557</v>
       </c>
       <c r="D29" t="n">
-        <v>-33.4</v>
+        <v>-0.1009143473544256</v>
       </c>
       <c r="E29" t="n">
-        <v>1115.56</v>
+        <v>0.01018370550196967</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.7</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33.93100440488091</v>
       </c>
       <c r="D30" t="n">
-        <v>-33.7</v>
+        <v>0.2310044048809061</v>
       </c>
       <c r="E30" t="n">
-        <v>1135.69</v>
+        <v>0.0533630350743816</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.1</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>34.69771747294202</v>
       </c>
       <c r="D31" t="n">
-        <v>-34.1</v>
+        <v>0.5977174729420227</v>
       </c>
       <c r="E31" t="n">
-        <v>1162.81</v>
+        <v>0.3572661774601977</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>34.72062645199188</v>
       </c>
       <c r="D32" t="n">
-        <v>-34.4</v>
+        <v>0.3206264519918847</v>
       </c>
       <c r="E32" t="n">
-        <v>1183.36</v>
+        <v>0.1028013217169043</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.9</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>35.21850464189565</v>
       </c>
       <c r="D33" t="n">
-        <v>-34.9</v>
+        <v>0.3185046418956503</v>
       </c>
       <c r="E33" t="n">
-        <v>1218.01</v>
+        <v>0.1014452069090764</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.3</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>35.05499915420738</v>
       </c>
       <c r="D34" t="n">
-        <v>-35.3</v>
+        <v>-0.2450008457926174</v>
       </c>
       <c r="E34" t="n">
-        <v>1246.09</v>
+        <v>0.06002541443909788</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.7</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>35.3473033739953</v>
       </c>
       <c r="D35" t="n">
-        <v>-35.7</v>
+        <v>-0.3526966260047004</v>
       </c>
       <c r="E35" t="n">
-        <v>1274.49</v>
+        <v>0.1243949099950995</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>35.98922756969985</v>
       </c>
       <c r="D36" t="n">
-        <v>-36.3</v>
+        <v>-0.3107724303001476</v>
       </c>
       <c r="E36" t="n">
-        <v>1317.69</v>
+        <v>0.09657950343466007</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>36.38170493970585</v>
       </c>
       <c r="D37" t="n">
-        <v>-36.8</v>
+        <v>-0.4182950602941489</v>
       </c>
       <c r="E37" t="n">
-        <v>1354.24</v>
+        <v>0.1749707574664856</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>37.41691575368267</v>
       </c>
       <c r="D38" t="n">
-        <v>-37.3</v>
+        <v>0.1169157536826759</v>
       </c>
       <c r="E38" t="n">
-        <v>1391.29</v>
+        <v>0.01366929345918815</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.9</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>37.95126721373015</v>
       </c>
       <c r="D39" t="n">
-        <v>-37.9</v>
+        <v>0.05126721373015641</v>
       </c>
       <c r="E39" t="n">
-        <v>1436.41</v>
+        <v>0.002628327203653538</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.5</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>38.5437647617419</v>
       </c>
       <c r="D40" t="n">
-        <v>-38.5</v>
+        <v>0.04376476174189747</v>
       </c>
       <c r="E40" t="n">
-        <v>1482.25</v>
+        <v>0.001915354370325053</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.9</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>39.41892405364155</v>
       </c>
       <c r="D41" t="n">
-        <v>-38.9</v>
+        <v>0.5189240536415483</v>
       </c>
       <c r="E41" t="n">
-        <v>1513.21</v>
+        <v>0.2692821734477764</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.4</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>40.13086809550075</v>
       </c>
       <c r="D42" t="n">
-        <v>-39.4</v>
+        <v>0.7308680955007532</v>
       </c>
       <c r="E42" t="n">
-        <v>1552.36</v>
+        <v>0.534168173020898</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>40.42224859150753</v>
       </c>
       <c r="D43" t="n">
-        <v>-39.9</v>
+        <v>0.5222485915075268</v>
       </c>
       <c r="E43" t="n">
-        <v>1592.01</v>
+        <v>0.2727435913315956</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.1</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>40.01027232520678</v>
       </c>
       <c r="D44" t="n">
-        <v>-40.1</v>
+        <v>-0.08972767479322385</v>
       </c>
       <c r="E44" t="n">
-        <v>1608.01</v>
+        <v>0.00805105562379854</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.6</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>41.15194085867312</v>
       </c>
       <c r="D45" t="n">
-        <v>-40.6</v>
+        <v>0.5519408586731203</v>
       </c>
       <c r="E45" t="n">
-        <v>1648.36</v>
+        <v>0.3046387114728213</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.9</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>41.37871835482554</v>
       </c>
       <c r="D46" t="n">
-        <v>-40.9</v>
+        <v>0.4787183548255456</v>
       </c>
       <c r="E46" t="n">
-        <v>1672.81</v>
+        <v>0.229171263246877</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>41.16526965467785</v>
       </c>
       <c r="D47" t="n">
-        <v>-41.2</v>
+        <v>-0.0347303453221528</v>
       </c>
       <c r="E47" t="n">
-        <v>1697.44</v>
+        <v>0.001206196886195981</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.5</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>40.90932046603844</v>
       </c>
       <c r="D48" t="n">
-        <v>-41.5</v>
+        <v>-0.5906795339615556</v>
       </c>
       <c r="E48" t="n">
-        <v>1722.25</v>
+        <v>0.3489023118410405</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.8</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>41.283508081798</v>
       </c>
       <c r="D49" t="n">
-        <v>-41.8</v>
+        <v>-0.516491918202</v>
       </c>
       <c r="E49" t="n">
-        <v>1747.24</v>
+        <v>0.2667639015679815</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.2</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>41.74291447674603</v>
       </c>
       <c r="D50" t="n">
-        <v>-42.2</v>
+        <v>-0.4570855232539728</v>
       </c>
       <c r="E50" t="n">
-        <v>1780.84</v>
+        <v>0.2089271755683581</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.7</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>42.06826020706399</v>
       </c>
       <c r="D51" t="n">
-        <v>-42.7</v>
+        <v>-0.6317397929360098</v>
       </c>
       <c r="E51" t="n">
-        <v>1823.29</v>
+        <v>0.3990951659788325</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1715.39</v>
+        <v>1.097033157294227</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>59704.6625</v>
+        <v>5.93160861708988</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1194.09325</v>
+        <v>0.1186321723417976</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_7.xlsx
+++ b/full/sliding_window_results_window_7.xlsx
@@ -463,13 +463,13 @@
         <v>29.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30.40247058788219</v>
+        <v>29.65568388359052</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6524705878821884</v>
+        <v>-0.09431611640948034</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4257178680513285</v>
+        <v>0.008895529814566648</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.84</v>
       </c>
       <c r="C3" t="n">
-        <v>29.84945777265597</v>
+        <v>29.85021190534634</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009457772655970587</v>
+        <v>0.01021190534633831</v>
       </c>
       <c r="E3" t="n">
-        <v>8.944946361202493e-05</v>
+        <v>0.000104283010802573</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.81</v>
       </c>
       <c r="C4" t="n">
-        <v>29.66142247796292</v>
+        <v>29.73375950682626</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1485775220370762</v>
+        <v>-0.07624049317373505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02207528005467786</v>
+        <v>0.00581261279937434</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.92</v>
       </c>
       <c r="C5" t="n">
-        <v>29.5982817534586</v>
+        <v>29.73741132313609</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3217182465414048</v>
+        <v>-0.182588676863908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1035026301576761</v>
+        <v>0.03333862491891262</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.98</v>
       </c>
       <c r="C6" t="n">
-        <v>29.85312025586845</v>
+        <v>29.94171638163823</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1268797441315463</v>
+        <v>-0.03828361836177407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01609846947088667</v>
+        <v>0.001465635434869965</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.04</v>
       </c>
       <c r="C7" t="n">
-        <v>30.06600351530143</v>
+        <v>30.071729328593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02600351530143286</v>
+        <v>0.03172932859300559</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0006761828080318527</v>
+        <v>0.001006750292962922</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.21</v>
       </c>
       <c r="C8" t="n">
-        <v>30.34908901132387</v>
+        <v>29.92353557505456</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1390890113238719</v>
+        <v>-0.2864644249454429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01934575307105215</v>
+        <v>0.08206186675932328</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.22</v>
       </c>
       <c r="C9" t="n">
-        <v>30.52594039433468</v>
+        <v>29.99273720722269</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3059403943346766</v>
+        <v>-0.2272627927773136</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0935995248856574</v>
+        <v>0.0516483769809442</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.38</v>
       </c>
       <c r="C10" t="n">
-        <v>30.35365911871458</v>
+        <v>30.06359699180335</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02634088128542089</v>
+        <v>-0.3164030081966445</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006938420268926366</v>
+        <v>0.1001108635958859</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.44</v>
       </c>
       <c r="C11" t="n">
-        <v>30.43898411740251</v>
+        <v>30.15212547007042</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.001015882597489082</v>
+        <v>-0.2878745299295851</v>
       </c>
       <c r="E11" t="n">
-        <v>1.032017451881164e-06</v>
+        <v>0.08287174498217957</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.48</v>
       </c>
       <c r="C12" t="n">
-        <v>30.55094216973905</v>
+        <v>30.40722003378083</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07094216973904466</v>
+        <v>-0.07277996621917282</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005032791447283424</v>
+        <v>0.005296923482863937</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.69</v>
       </c>
       <c r="C13" t="n">
-        <v>30.68086014304607</v>
+        <v>30.61979783645333</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.009139856953929382</v>
+        <v>-0.07020216354666786</v>
       </c>
       <c r="E13" t="n">
-        <v>8.353698513829128e-05</v>
+        <v>0.004928343766633102</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.75</v>
       </c>
       <c r="C14" t="n">
-        <v>30.27902283158048</v>
+        <v>30.2915422588236</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4709771684195232</v>
+        <v>-0.4584577411763959</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2218194931724719</v>
+        <v>0.2101835004445632</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.94</v>
       </c>
       <c r="C15" t="n">
-        <v>30.38232876759964</v>
+        <v>30.63560919358222</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.557671232400363</v>
+        <v>-0.304390806417782</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3109972034469397</v>
+        <v>0.09265376303166767</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.95</v>
       </c>
       <c r="C16" t="n">
-        <v>30.69458768077862</v>
+        <v>30.76690868959878</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2554123192213815</v>
+        <v>-0.183091310401224</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06523545281004489</v>
+        <v>0.03352242794443733</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.02</v>
       </c>
       <c r="C17" t="n">
-        <v>31.06272285481336</v>
+        <v>30.99395684544406</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04272285481335913</v>
+        <v>-0.02604315455593564</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001825242323403364</v>
+        <v>0.0006782458992243515</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.12</v>
       </c>
       <c r="C18" t="n">
-        <v>31.35281011065088</v>
+        <v>31.15507157847749</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2328101106508811</v>
+        <v>0.03507157847749198</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0542005476212755</v>
+        <v>0.001230015616902879</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.28</v>
       </c>
       <c r="C19" t="n">
-        <v>31.33141430812179</v>
+        <v>31.30042908387883</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05141430812179237</v>
+        <v>0.02042908387882392</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002643431079642605</v>
+        <v>0.0004173474681280233</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.38</v>
       </c>
       <c r="C20" t="n">
-        <v>31.6087785071903</v>
+        <v>31.41254549469874</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2287785071902988</v>
+        <v>0.0325454946987449</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0523396053522216</v>
+        <v>0.001059209225186033</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.58</v>
       </c>
       <c r="C21" t="n">
-        <v>31.92626103420487</v>
+        <v>31.60508101252302</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3462610342048755</v>
+        <v>0.02508101252301742</v>
       </c>
       <c r="E21" t="n">
-        <v>0.11989670380863</v>
+        <v>0.0006290571891797566</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.65</v>
       </c>
       <c r="C22" t="n">
-        <v>31.9100204118511</v>
+        <v>31.52223150751452</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2600204118511016</v>
+        <v>-0.1277684924854761</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06761061457921649</v>
+        <v>0.01632478767201115</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.88</v>
       </c>
       <c r="C23" t="n">
-        <v>31.59474956815411</v>
+        <v>31.75428833836477</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2852504318458919</v>
+        <v>-0.1257116616352292</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08136780886826785</v>
+        <v>0.01580342187109035</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.28</v>
       </c>
       <c r="C24" t="n">
-        <v>32.11077502296926</v>
+        <v>32.07426206282727</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1692249770307441</v>
+        <v>-0.205737937172735</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02863709285105588</v>
+        <v>0.04232809879209227</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.45</v>
       </c>
       <c r="C25" t="n">
-        <v>32.1607344515993</v>
+        <v>32.05159442638237</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2892655484007065</v>
+        <v>-0.3984055736176302</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08367455749156148</v>
+        <v>0.158727001089593</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.85</v>
       </c>
       <c r="C26" t="n">
-        <v>33.26761652402123</v>
+        <v>33.09318230853673</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4176165240212271</v>
+        <v>0.2431823085367242</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1744035611355721</v>
+        <v>0.05913763518525051</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.9</v>
       </c>
       <c r="C27" t="n">
-        <v>32.95359507319187</v>
+        <v>32.72056146722885</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05359507319187173</v>
+        <v>-0.179438532771151</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002872431870442088</v>
+        <v>0.03219818704306342</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.1</v>
       </c>
       <c r="C28" t="n">
-        <v>33.28701813607838</v>
+        <v>33.02529646120471</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1870181360783789</v>
+        <v>-0.07470353879529057</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03497578322223106</v>
+        <v>0.005580618708539483</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.4</v>
       </c>
       <c r="C29" t="n">
-        <v>33.29908565264557</v>
+        <v>33.16077020649679</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1009143473544256</v>
+        <v>-0.2392297935032062</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01018370550196967</v>
+        <v>0.05723089409958666</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.7</v>
       </c>
       <c r="C30" t="n">
-        <v>33.93100440488091</v>
+        <v>33.56588822418949</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2310044048809061</v>
+        <v>-0.134111775810517</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0533630350743816</v>
+        <v>0.01798596841105038</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.1</v>
       </c>
       <c r="C31" t="n">
-        <v>34.69771747294202</v>
+        <v>34.11588261877039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5977174729420227</v>
+        <v>0.01588261877039088</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3572661774601977</v>
+        <v>0.0002522575790055726</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.4</v>
       </c>
       <c r="C32" t="n">
-        <v>34.72062645199188</v>
+        <v>34.20668080773725</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3206264519918847</v>
+        <v>-0.1933191922627486</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1028013217169043</v>
+        <v>0.03737231009712157</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.9</v>
       </c>
       <c r="C33" t="n">
-        <v>35.21850464189565</v>
+        <v>35.01255725601396</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3185046418956503</v>
+        <v>0.1125572560139645</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1014452069090764</v>
+        <v>0.01266913588139315</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.3</v>
       </c>
       <c r="C34" t="n">
-        <v>35.05499915420738</v>
+        <v>34.83099465470639</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2450008457926174</v>
+        <v>-0.4690053452936098</v>
       </c>
       <c r="E34" t="n">
-        <v>0.06002541443909788</v>
+        <v>0.2199660139139782</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.7</v>
       </c>
       <c r="C35" t="n">
-        <v>35.3473033739953</v>
+        <v>35.31468199164702</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3526966260047004</v>
+        <v>-0.3853180083529821</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1243949099950995</v>
+        <v>0.1484699675611088</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.3</v>
       </c>
       <c r="C36" t="n">
-        <v>35.98922756969985</v>
+        <v>36.17131539447819</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3107724303001476</v>
+        <v>-0.128684605521812</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09657950343466007</v>
+        <v>0.01655972769830438</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.8</v>
       </c>
       <c r="C37" t="n">
-        <v>36.38170493970585</v>
+        <v>36.59280475428218</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4182950602941489</v>
+        <v>-0.2071952457178199</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1749707574664856</v>
+        <v>0.04292986984806776</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.3</v>
       </c>
       <c r="C38" t="n">
-        <v>37.41691575368267</v>
+        <v>37.26256779863932</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1169157536826759</v>
+        <v>-0.03743220136067293</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01366929345918815</v>
+        <v>0.001401169698705965</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.9</v>
       </c>
       <c r="C39" t="n">
-        <v>37.95126721373015</v>
+        <v>37.86754046597422</v>
       </c>
       <c r="D39" t="n">
-        <v>0.05126721373015641</v>
+        <v>-0.03245953402578294</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002628327203653538</v>
+        <v>0.001053621349170961</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.5</v>
       </c>
       <c r="C40" t="n">
-        <v>38.5437647617419</v>
+        <v>38.25742578974995</v>
       </c>
       <c r="D40" t="n">
-        <v>0.04376476174189747</v>
+        <v>-0.242574210250055</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001915354370325053</v>
+        <v>0.05884224747843788</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.9</v>
       </c>
       <c r="C41" t="n">
-        <v>39.41892405364155</v>
+        <v>38.67455509081069</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5189240536415483</v>
+        <v>-0.2254449091893065</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2692821734477764</v>
+        <v>0.05082540707937465</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.4</v>
       </c>
       <c r="C42" t="n">
-        <v>40.13086809550075</v>
+        <v>39.22313901282494</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7308680955007532</v>
+        <v>-0.1768609871750613</v>
       </c>
       <c r="E42" t="n">
-        <v>0.534168173020898</v>
+        <v>0.03127980878453718</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.9</v>
       </c>
       <c r="C43" t="n">
-        <v>40.42224859150753</v>
+        <v>39.56601804535462</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5222485915075268</v>
+        <v>-0.3339819546453739</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2727435913315956</v>
+        <v>0.1115439460287446</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.1</v>
       </c>
       <c r="C44" t="n">
-        <v>40.01027232520678</v>
+        <v>40.29440674145924</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.08972767479322385</v>
+        <v>0.1944067414592396</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00805105562379854</v>
+        <v>0.03779398112479965</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.6</v>
       </c>
       <c r="C45" t="n">
-        <v>41.15194085867312</v>
+        <v>40.46544552621783</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5519408586731203</v>
+        <v>-0.134554473782174</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3046387114728213</v>
+        <v>0.01810490641479775</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.9</v>
       </c>
       <c r="C46" t="n">
-        <v>41.37871835482554</v>
+        <v>41.00287925752529</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4787183548255456</v>
+        <v>0.1028792575252879</v>
       </c>
       <c r="E46" t="n">
-        <v>0.229171263246877</v>
+        <v>0.01058414162895451</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.2</v>
       </c>
       <c r="C47" t="n">
-        <v>41.16526965467785</v>
+        <v>41.44111360606216</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0347303453221528</v>
+        <v>0.2411136060621573</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001206196886195981</v>
+        <v>0.05813577102829716</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.5</v>
       </c>
       <c r="C48" t="n">
-        <v>40.90932046603844</v>
+        <v>41.18337414111874</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5906795339615556</v>
+        <v>-0.3166258588812596</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3489023118410405</v>
+        <v>0.1002519345122953</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.8</v>
       </c>
       <c r="C49" t="n">
-        <v>41.283508081798</v>
+        <v>41.45935521381426</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.516491918202</v>
+        <v>-0.3406447861857345</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2667639015679815</v>
+        <v>0.1160388703555248</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.2</v>
       </c>
       <c r="C50" t="n">
-        <v>41.74291447674603</v>
+        <v>41.81547616390429</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4570855232539728</v>
+        <v>-0.3845238360957097</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2089271755683581</v>
+        <v>0.1478585805257602</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.7</v>
       </c>
       <c r="C51" t="n">
-        <v>42.06826020706399</v>
+        <v>42.42338389152952</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6317397929360098</v>
+        <v>-0.2766161084704848</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3990951659788325</v>
+        <v>0.07651647146535501</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.097033157294227</v>
+        <v>-6.929657174091698</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.93160861708988</v>
+        <v>2.42168187558462</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1186321723417976</v>
+        <v>0.04843363751169241</v>
       </c>
     </row>
   </sheetData>
